--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>46191</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45707</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>45085</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45107</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>46205</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44865</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>45602</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>45414</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>45630</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45635</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45795</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>45609</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45979</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>46205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>45713</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45630</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>45678</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45106</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>45685</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>45831</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45713</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>45635</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>44865</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>46091</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>44784</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>44473</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>44841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45891</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>4</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>45795</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>44648</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>45595</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>46185</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>46111</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>46260</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>45555</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45922</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45982</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44841</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45071</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45709</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>45081</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>45849</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44533</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44606</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>44550</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44606</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44462</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>44958</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>45002</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>45280</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>45107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45160</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>45247</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>45594</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>45589</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>45728</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45548</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45155</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44890</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44897</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44518</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45589</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45226</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44907</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45280</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45103</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44734</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44989</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45702</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45191</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45029</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44978</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45400</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45107</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45602</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44978</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45545</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45027</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>44505</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>45069</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44606</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45681</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45001</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45700</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>45722</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>45110</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44546</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45697</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>45086</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>44882</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>44879</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45491</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45890</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44914</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45104</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45899</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45901</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45635</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45090</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44845</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>44638</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45749</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45758</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45758</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>45916</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45922</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44855</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45259</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45926</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>44879</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>46146</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45953</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45953</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44466</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>46151</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45625</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45639</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45959</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>45959</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45961</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44657</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>44657</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45966</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44657</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45545</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>45966</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>45054</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44546</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45198</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45414</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45747</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45979</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45979</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44852</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45980</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45980</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45980</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>45980</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45980</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45982</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45056</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>45982</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>44468</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45982</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45982</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45982</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45981</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45156</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>44978</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45548</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45159</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>44473</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45154</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45678</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44546</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>46164</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>46003</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>46002</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>46164</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16762,7 +16762,7 @@
         <v>46007</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>46148</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>45371</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45376</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>45371</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>45817</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45371</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45371</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>46169</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>44797</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>46034</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>46034</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>46035</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>45219</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>46034</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45611</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44869</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>44841</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46043</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>46043</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>46042</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>46045</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44917</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45979</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>46175</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46175</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45709</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>46178</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45491</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45999</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46178</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45722</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>46178</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>46178</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>46178</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45155</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44916</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>46062</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         <v>44994</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
         <v>44538</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44978</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>46078</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45177</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>46083</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>46185</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>46083</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44719</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>44918</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>46185</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>46085</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45034</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45548</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45420</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>46185</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>46185</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>46185</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46185</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>44999</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>44834</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45609</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>46099</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>46099</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>46098</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45804</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>46014</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45707</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45002</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45804</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>44719</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45602</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>45029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>46128</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46128</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46129</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45589</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>46129</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>44719</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>46128</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>45520</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45400</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45559</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45602</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45518</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45568</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>46185</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45198</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44866</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45681</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>44974</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>46205</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>46247</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>45043</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45159</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45635</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>45124</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>46248</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>46251</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>46248</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>46248</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>46248</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44925</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>46248</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>46248</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>46248</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44895</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44992</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46248</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>46248</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>46248</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>46253</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>46253</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44984</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>46253</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45548</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>46253</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>46253</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46209</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46175</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>46253</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>46209</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>46211</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>46211</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>46211</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46253</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45063</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44893</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>46245</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45306</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45520</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45520</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>46223</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>44731</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>46267</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27088,7 +27088,7 @@
         <v>45804</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>45937</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45804</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>45804</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45804</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>44531</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>46225</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44935</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45182</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>46252</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>46225</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45697</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>46261</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>46227</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>45715</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45715</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>46254</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45634</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>44992</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>46216</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45364</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45400</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>45279</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>46280</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>46238</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>46238</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29069,7 +29069,7 @@
         <v>46225</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>44900</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44866</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45794</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>46239</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         <v>45794</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29512,7 +29512,7 @@
         <v>46239</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>46240</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>44886</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>45815</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45815</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45818</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>45831</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>45414</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>45414</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45414</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>45414</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45860</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30393,7 +30393,7 @@
         <v>45860</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45860</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>45860</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>45875</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44607</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44943</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45957</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45958</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45609</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45678</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45825</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44841</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>46091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>44865</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44473</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45795</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45891</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44648</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45008</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46290</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45709</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45081</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>45982</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45071</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44841</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45555</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45849</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44533</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44935</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45400</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45400</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45110</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>44866</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44978</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45371</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45371</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45371</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45371</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45376</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>45794</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45794</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>46034</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>46034</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>46034</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>46035</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45890</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45280</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45611</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>46043</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>46042</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44916</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>46043</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45901</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>46045</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45899</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45198</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45916</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>46062</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45922</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44907</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45926</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>46078</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>46083</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>46085</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45247</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>45034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44473</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45589</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44886</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45054</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>46099</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>46099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>46098</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>46014</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45804</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45259</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44505</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45639</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44890</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45959</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45959</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44797</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45961</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45609</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45966</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45594</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45414</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45002</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44518</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>46129</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>46128</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>46129</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>46128</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45027</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45980</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45980</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45980</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45979</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45980</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45979</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45980</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45982</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45982</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45982</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45982</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45982</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>45981</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45156</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44734</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45722</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>44719</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45697</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45678</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44719</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45815</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45815</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45625</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44989</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45818</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46002</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>46003</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45086</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>45191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45758</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>46007</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44879</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45681</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45758</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44866</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45001</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45491</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45306</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44532</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45226</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>46146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44879</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45831</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45182</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45414</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45414</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45414</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45280</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45414</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>46151</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44855</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44466</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45219</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>44538</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45103</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45559</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45104</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44531</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45069</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>44852</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>46164</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>46164</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45548</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46148</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45860</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45860</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44918</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45860</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45860</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45979</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45709</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44914</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>46175</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>45999</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45722</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>46178</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45124</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>46178</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>46178</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>46178</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>46178</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44546</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>46185</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>46185</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>46185</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>46185</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>46185</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>46185</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46185</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45589</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44999</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45875</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45029</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44546</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45056</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45518</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45159</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45177</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45198</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45545</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>46185</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46205</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>46209</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45926</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>44546</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>46209</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>46251</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>46175</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46253</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46253</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>46211</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>46253</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>46253</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>46253</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46253</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45159</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46253</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45154</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45681</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45702</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>44719</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>45107</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44731</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44657</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45520</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>46223</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>46267</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>46225</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45937</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46225</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44841</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>46227</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44893</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>46252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>44869</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>46225</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>46280</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44974</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>46238</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45825</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>46239</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45520</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45520</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45602</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>46238</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>46240</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45548</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>44845</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44925</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45002</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44606</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45568</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>46211</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>46245</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45063</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45953</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>46248</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>46248</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>46248</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>46248</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>46248</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>44994</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45804</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>46248</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>46248</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>46248</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>45715</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45715</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45804</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45107</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>46216</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46247</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46248</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46248</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46261</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45602</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45707</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>46239</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46290</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>46254</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45804</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>44882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>44978</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45548</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>44468</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45029</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>44890</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44917</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>45602</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>44897</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45420</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45160</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>44984</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44657</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>44657</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44841</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45635</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45749</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>44978</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>45589</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45155</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45090</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45728</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45548</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45697</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>45634</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>44992</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45279</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>45364</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45400</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44900</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44607</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>44943</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45957</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45609</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45678</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45106</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45825</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44841</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>46091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>44865</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44473</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45795</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45891</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44648</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45008</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>45595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46290</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45709</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>45081</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>45982</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45071</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>44841</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45555</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45849</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44533</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>45043</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>44834</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>44935</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45400</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>45400</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45110</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>44866</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44978</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45371</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45371</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45371</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45371</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45376</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>45794</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45794</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>45491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>46034</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>46034</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>46034</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>46035</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45890</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>45280</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45611</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>46043</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>46042</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44916</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>46043</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45901</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>46045</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45899</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45198</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45916</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>46062</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>45922</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44907</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45926</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>46078</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>46083</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>46085</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>45247</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>45034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44473</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45589</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44886</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45054</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>46099</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>46099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>46098</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>46014</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45804</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45259</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44505</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45639</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44890</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45959</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45959</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44797</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45961</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45609</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45966</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45594</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45414</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45002</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44518</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>46129</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>46128</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>46128</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>46129</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>46128</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45027</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45980</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45980</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45980</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45979</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45980</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45979</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45980</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45982</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45982</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45982</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45982</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45982</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>45981</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45156</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44734</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>45722</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>44719</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45697</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45678</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44719</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45700</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45815</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45815</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45625</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44989</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45818</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46002</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>46003</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45086</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>45191</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45758</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>46007</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44879</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>45681</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45758</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44866</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45001</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45491</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45306</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44532</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45226</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>46146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44879</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45831</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45182</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45414</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45414</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45414</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45280</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45414</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>46151</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44855</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>44466</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45219</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>44538</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45103</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>45559</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45104</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44531</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45069</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>44852</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>46164</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>46164</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45548</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46148</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45860</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45860</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44918</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45860</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45860</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45979</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45709</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44914</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>46175</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>45999</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45722</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>46178</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45124</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>46178</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>46178</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>46178</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>46178</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44546</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>46185</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>46185</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>46185</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>46185</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>46185</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>46185</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>46185</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46185</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45589</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44999</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45875</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45029</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44546</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45056</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45518</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45159</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45177</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45198</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45545</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>46185</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46205</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>46209</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45926</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>44546</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>46209</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>46251</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>46175</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>46253</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46253</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>46211</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>46253</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>46253</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>46253</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46253</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45159</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46253</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45154</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45681</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45702</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>44719</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>45107</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44731</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>44657</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45520</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>46223</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>46267</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>46225</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45937</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>46225</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44841</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>46227</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44893</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>46252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>44869</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>46225</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>46280</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44974</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>46238</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45825</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>46239</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45520</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45520</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>45602</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>46238</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25125,7 +25125,7 @@
         <v>46240</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>45548</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>44845</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44925</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45002</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44606</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45568</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>46211</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>46245</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45063</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45953</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>46248</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>46248</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>46248</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>46248</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>46248</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>44994</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45804</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>46248</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>46248</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>46248</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>45715</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45715</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45804</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45107</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>46216</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46247</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46248</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>46248</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46261</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45602</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45707</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>46239</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46290</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>46254</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45804</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>44882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>44978</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45548</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>44468</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>45029</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>44890</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44917</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>45602</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>44897</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45420</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45160</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>44984</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44657</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>44657</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44841</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45635</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45749</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>44978</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>45589</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45155</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45090</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45728</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45548</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45697</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>45634</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>44992</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45279</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>45364</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45400</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44900</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44607</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>44943</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>45957</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44621</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45609</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44841</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>45678</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45831</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45685</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>46091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>44865</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44473</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45891</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44648</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45008</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>46111</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46290</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>45982</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45849</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44841</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45071</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45709</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45081</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44533</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45107</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>45160</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45594</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45247</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45548</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>45155</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>45728</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>44908</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44532</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>46003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45589</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>46007</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45364</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44841</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45400</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45279</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45371</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45376</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45371</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45371</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45371</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45890</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45280</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45899</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>46034</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>46034</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44907</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>46035</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45103</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>46034</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45611</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>46043</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>46043</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>46042</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44900</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44866</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45794</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45794</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45916</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44989</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44734</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45922</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45926</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45702</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>46062</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44886</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45191</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45029</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44978</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45400</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>46078</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45602</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>46083</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>46083</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>46085</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45034</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45639</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44978</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45959</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45545</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45961</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44505</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45027</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45069</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45815</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45966</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45966</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45815</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44606</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>46099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>46099</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45001</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>46098</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45818</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45979</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45979</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45980</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45980</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45980</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45980</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45980</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45982</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45982</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45982</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45982</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45982</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45981</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45986</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45986</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>45681</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45110</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>45678</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>46128</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46128</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>46129</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46129</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>46128</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44546</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45831</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45086</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44882</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45414</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44879</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45414</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45491</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45414</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45414</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44866</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>44914</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45104</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45635</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45700</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45090</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44845</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45697</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45749</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44855</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45860</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45860</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45860</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45860</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45758</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45758</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>46146</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45625</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46151</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44657</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44657</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>44657</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45545</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45054</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44546</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45198</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45875</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45414</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>46164</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>44852</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>46164</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45056</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>46148</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45156</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>44978</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45548</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45159</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44473</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>45979</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>46175</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>46175</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45709</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>46178</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45999</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>46178</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45722</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>46178</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>46178</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>46178</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44546</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>46185</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>46185</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>46185</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>46185</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>46185</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>46185</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46185</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44999</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>44797</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>46185</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>46205</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44869</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44841</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45926</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46209</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>46175</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>46209</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>46211</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44917</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45491</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45155</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45520</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44916</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>46223</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>46267</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45937</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>44994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44538</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>46225</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44978</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46225</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>45177</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44719</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>44918</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45548</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45420</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45825</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>46280</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>46238</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>46225</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44834</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>46239</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>46240</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45609</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45953</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>46211</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>46245</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44719</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45602</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>46261</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46216</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>46248</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>46248</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>46248</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>46248</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>45029</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45804</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>46239</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45715</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45715</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45589</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45804</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44719</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>46248</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45804</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45707</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45520</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>46247</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>46290</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>46248</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46248</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>46248</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>46248</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45400</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>45559</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>45602</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45518</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>45568</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45198</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>46251</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>46253</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>46014</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45804</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>45681</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44974</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45722</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44890</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45043</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45635</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45124</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45804</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>46253</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>46248</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>46252</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>46234</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44925</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>46254</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>46227</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>46253</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>46253</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>46253</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>46253</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>44895</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44992</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44984</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45548</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45063</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44893</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45306</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45520</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>44731</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>44531</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>44935</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45697</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45634</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>44607</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44943</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45957</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44621</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45609</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44841</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>45678</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45831</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45685</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45635</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>45713</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>46091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>44865</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44473</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45891</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44648</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>45008</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>46111</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>46290</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>45982</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45849</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>44546</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>44841</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45071</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45709</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45081</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44533</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45107</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>45160</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45594</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45247</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45548</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>45155</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>45728</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>44908</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44532</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>46003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>46002</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45589</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44518</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>46007</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45364</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44841</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45400</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45279</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>45371</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45376</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45371</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45817</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>45371</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45371</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>45890</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45280</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45899</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>46034</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>46034</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44907</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>46035</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45103</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>46034</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45611</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>46043</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>46043</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>46042</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44900</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44866</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45794</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>45794</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45916</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44989</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44734</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45922</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45926</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45702</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>46062</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44886</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45191</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45029</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44978</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45400</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>46078</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45107</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45602</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>46083</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>46083</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>46085</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45034</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45639</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44978</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45959</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45545</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45961</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44505</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45027</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45069</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>45815</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45966</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45966</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45815</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44606</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>46099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>46099</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45001</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>46098</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45818</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45979</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45979</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45980</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45980</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>45980</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45980</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45980</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45982</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45982</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45982</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45982</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45982</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45981</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45986</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45986</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>45681</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45110</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>45678</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>46128</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46128</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>46129</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>46129</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>46128</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44546</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>45831</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45086</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44882</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45414</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44879</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45414</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45491</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45414</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45414</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44866</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>44914</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45104</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45635</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45700</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45090</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44845</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>45697</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45749</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44855</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>45259</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45860</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45860</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44879</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45860</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45860</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45758</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45758</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>46146</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45625</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46151</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44657</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44657</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>44657</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45545</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45054</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44546</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45198</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45875</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45414</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>46164</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>44852</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>46164</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45056</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>46148</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>45156</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>44978</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45548</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45159</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44473</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>45979</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>46175</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>46175</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45709</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20215,7 +20215,7 @@
         <v>46178</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45999</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>46178</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45722</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>46178</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>46178</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>46178</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44546</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>46185</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>46185</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>46185</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>46185</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>46185</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>46185</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46185</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44999</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>44797</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>46185</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>46205</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44869</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44841</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45926</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46209</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>46175</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>46209</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>46211</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44917</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45491</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45155</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45520</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44916</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>46223</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>46267</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45937</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>44994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44538</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>46225</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>44978</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>46225</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>45177</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44719</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>44918</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45548</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45420</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45825</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>46280</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>46238</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>46238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>46225</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44834</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>46239</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>46240</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>45609</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45953</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45002</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>46211</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>46245</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44719</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>45602</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>46261</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>46216</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>46248</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>46248</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>46248</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>46248</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>45029</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45804</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>46239</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45715</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45715</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45589</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45804</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44719</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>46248</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45804</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45804</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45707</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45520</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>46247</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>46290</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>46248</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>46248</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>46248</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>46248</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45400</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>45559</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>45602</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45518</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>45568</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>45198</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>46251</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>46253</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>46014</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45804</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>45681</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44974</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45722</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44890</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45043</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45635</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45124</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45804</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>46253</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>46248</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>46252</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>46234</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>44925</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>46254</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>46227</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>46253</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>46253</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>46253</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>46253</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>44895</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44992</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44984</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45548</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45063</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44893</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45306</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45520</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>44731</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>44531</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>44935</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45697</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45634</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>44607</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44943</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45957</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45609</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45678</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>44865</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46091</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45891</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45795</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>44648</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>45008</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45595</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>46290</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>46260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44841</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45709</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>45081</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>45849</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45982</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45071</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>44533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44501</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44879</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45182</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45219</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45160</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44538</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44935</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44984</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>45103</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45559</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45104</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44531</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45400</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45069</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>45043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>44852</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45400</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44834</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>44657</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44657</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44958</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44841</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45548</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45749</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>45110</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45589</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44895</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>44978</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45155</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45090</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44914</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45901</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45899</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45155</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>45280</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45635</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45728</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>45548</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44916</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>45124</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45697</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>45916</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44546</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44908</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45198</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>45589</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>45634</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45279</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45364</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44907</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>45926</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>45400</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>44900</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>44546</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>44866</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45794</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45794</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45589</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45056</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45518</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45159</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45177</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45198</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>45545</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44546</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>44886</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>44992</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45259</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44505</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45815</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45815</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>45818</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44890</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44797</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44978</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>45609</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>45154</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45594</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45831</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>45681</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45414</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45639</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45959</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45959</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45002</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45414</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45414</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44518</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45414</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45414</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45702</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44719</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45961</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45107</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45966</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45966</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44731</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45156</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44657</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44734</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44719</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44719</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45860</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>45860</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>45860</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>45860</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45625</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>44989</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>44841</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45086</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45980</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45980</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>44893</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45545</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45191</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45979</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44869</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45980</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45979</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45980</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45875</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45982</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>44879</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45982</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45982</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45681</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45982</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45982</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45981</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>46099</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>46099</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45986</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45001</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45986</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45986</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45491</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44974</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>46098</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45306</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45520</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45520</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45602</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44532</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45226</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45548</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44845</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45678</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>44925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45002</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44606</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>46129</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>46128</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>46128</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>46129</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>46128</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>46002</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45568</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>46003</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45063</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46007</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>44994</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45107</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45697</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45371</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45371</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45371</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45371</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45376</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45602</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45817</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45700</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>44882</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>44978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>46034</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46034</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45548</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45758</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45029</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>46035</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45611</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>46043</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>46042</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45758</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>44890</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>46043</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44866</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>46045</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44917</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>46062</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>46146</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>46078</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>46151</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>46083</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>46083</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>46085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45034</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46164</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>46164</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46148</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46175</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45979</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45709</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>46175</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45999</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45722</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>46178</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46178</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>46178</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>46178</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>46178</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46185</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>46185</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>46185</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>46185</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>46185</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>46185</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>46185</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44999</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>46185</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>46205</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>46209</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46209</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>46175</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>46211</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45520</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>46223</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>46267</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46225</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46225</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46225</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46280</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>46238</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>46239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>46238</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>46240</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>46211</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>46245</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45953</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45804</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45804</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45715</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45715</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45804</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>46216</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>46247</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>46239</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>46290</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45804</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>46248</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>46248</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>46248</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>46248</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46248</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46248</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46248</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>46248</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46248</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>46253</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>46253</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>46251</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>46253</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>46253</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>46253</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46253</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>45722</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>46254</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45707</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>46248</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>46227</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>46252</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>46234</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45804</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45825</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45926</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>46014</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45937</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>46302</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>46261</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>45804</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>46302</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44607</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>44943</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45609</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45630</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>45678</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45831</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>44865</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46091</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44784</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45891</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45795</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>44841</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>44518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>44648</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>45008</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45595</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>46290</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>46260</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44841</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45922</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45709</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
         <v>45081</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>45849</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45982</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45071</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>44533</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>44501</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>44879</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45602</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45182</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>44855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44897</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45219</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45160</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44538</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44935</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44984</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>45103</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>45559</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45104</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44531</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45400</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45069</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>45043</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>44852</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45400</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44834</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>44657</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44657</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44958</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44841</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45635</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45548</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45749</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>45110</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>45589</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44895</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>44978</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>45155</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45090</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44914</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>45901</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>45899</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45155</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>45280</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45635</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45728</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>45548</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44916</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>45124</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45697</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>45916</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44546</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44908</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45198</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>45922</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>45589</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>45634</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>44992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>45279</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45364</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44907</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>45926</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>45400</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>45029</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>44900</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>44546</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>44866</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45794</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45794</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>45247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45589</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45056</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45518</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45159</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45177</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45198</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>45545</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>44546</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>44886</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>44992</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45259</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44505</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45815</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45815</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>45818</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44890</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44797</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44978</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>45609</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>45154</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45594</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45831</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>45681</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45414</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45639</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45959</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45959</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45002</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45414</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45414</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44518</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45414</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>45414</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45702</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44719</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45961</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45107</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45966</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45966</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44731</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45156</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>44657</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>44734</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44719</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44719</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45860</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>45860</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>45860</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>45860</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45625</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>44989</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>44841</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>45086</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45980</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45980</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>44893</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45545</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45191</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45979</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>44869</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45980</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45979</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45980</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45875</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45982</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>44879</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45982</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45982</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45681</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45982</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45982</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45981</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>46099</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>46099</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45986</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45001</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>45986</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45986</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45491</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44974</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>46098</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45306</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45520</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45520</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45602</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>44532</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45226</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45548</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44845</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45678</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>44925</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>45002</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44606</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>46129</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>46128</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>46128</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>46129</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>46128</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>46002</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45568</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>46003</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45063</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46007</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>44994</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45107</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45697</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45371</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45371</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45371</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45371</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45376</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45602</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45817</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45700</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>44882</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>44978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>46034</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>46034</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46034</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45548</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45758</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45029</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>46035</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45611</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>46043</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>46042</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45758</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>44890</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>46043</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44866</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>46045</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44917</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>46062</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>46146</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>46078</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>46151</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>46083</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>46083</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>46085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45034</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>46164</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>46164</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>46148</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>46175</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45979</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45709</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>46175</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45999</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45722</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>46178</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46178</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>46178</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>46178</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>46178</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46185</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>46185</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>46185</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>46185</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>46185</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>46185</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>46185</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44999</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>46185</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>46205</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>46209</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>46209</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>46175</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>46211</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>45520</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>46223</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>46267</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46225</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46225</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46225</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         <v>46280</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>46238</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26400,7 +26400,7 @@
         <v>46239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>46238</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>46240</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>46211</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26692,7 +26692,7 @@
         <v>46245</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26765,7 +26765,7 @@
         <v>45953</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26838,7 +26838,7 @@
         <v>45804</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45804</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45715</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>45715</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45804</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>46216</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>46247</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>46239</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>46290</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45804</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>46248</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>46248</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>46248</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>46248</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46248</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46248</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46248</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>46248</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>46248</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>46253</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>46253</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>46251</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>46253</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>46253</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>46253</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46253</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>45722</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>46254</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45707</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>46248</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>46227</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>46252</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>46234</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45804</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45825</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45926</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>46014</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45937</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29775,7 +29775,7 @@
         <v>46302</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>46261</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29921,7 +29921,7 @@
         <v>45804</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>46302</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44607</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>44943</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30296,7 +30296,7 @@
         <v>45957</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44621</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45667</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46185</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45609</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45979</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46308</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>46205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45630</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>44841</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45678</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45831</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45713</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>44865</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>46091</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44784</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>45891</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>44648</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45008</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>46290</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>46260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45982</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>44841</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45709</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45081</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45849</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44533</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>45002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45160</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45280</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45107</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45594</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>45247</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>45548</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>45728</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45155</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45589</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44908</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>44890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44532</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44518</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45589</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44841</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45226</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44907</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45103</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44734</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44989</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>45702</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>44978</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45400</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45029</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45602</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44978</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45545</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45027</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44505</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45069</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44606</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>45001</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45681</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45700</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45697</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45110</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45890</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45086</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44882</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44879</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45899</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45901</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45758</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45491</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>45758</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>44914</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45104</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45916</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45635</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>46146</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45922</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44845</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45926</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>46151</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>44855</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45259</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44879</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45639</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45959</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45959</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45961</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45966</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45966</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45625</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45979</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45979</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45980</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45980</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45980</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45980</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>46164</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45982</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44657</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44657</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45982</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45982</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45982</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45982</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45981</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45986</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45986</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44657</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45545</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>46164</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45054</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44546</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45414</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>46148</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45678</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44852</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>46003</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45056</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>46002</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45156</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46007</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44978</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45548</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45159</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45154</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45371</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45376</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45371</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45817</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45371</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45371</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>46175</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>44546</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>46034</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>46034</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46035</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45709</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>46034</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45611</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45999</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45722</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>46178</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>46178</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46043</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>46043</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>46042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44797</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>46185</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>46185</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>46185</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46185</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>46185</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>46185</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>46078</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>46185</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>46185</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>45219</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44869</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46083</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44841</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>46083</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>46085</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45034</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44999</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44917</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>46099</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>46099</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>46098</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45491</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45155</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44916</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>44994</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>44538</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>44978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46128</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>46129</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>46129</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>46128</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>46185</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>46205</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44719</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>44918</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45548</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>45420</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44866</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44834</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45609</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>46209</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>46209</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>46211</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45002</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45520</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>46223</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>46225</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>46225</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44719</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45602</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45029</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>45589</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44719</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45520</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45400</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45559</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45602</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45518</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45568</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45198</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45681</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44974</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46280</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>46238</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46238</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>46225</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>44890</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45043</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45159</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45635</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45124</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>46239</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>46240</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44925</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45953</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44895</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44992</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44984</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>46211</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45548</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>46245</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>46216</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46248</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46248</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>46248</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46248</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45804</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>46239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45715</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45715</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45063</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45804</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>46248</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44893</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45804</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45804</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>46247</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46290</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>46248</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>46248</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>46248</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46248</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45306</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>45520</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>46251</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>46253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44731</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45722</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46253</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>44531</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>46248</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>46227</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>46253</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>46253</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46253</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46253</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>46253</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>44935</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45182</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45707</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45697</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>46234</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45634</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>46252</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45364</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45400</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45279</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46307</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44900</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44866</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45794</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45980</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>46302</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45794</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>46307</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>46307</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45804</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>46014</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>46308</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>46309</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>46309</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>46309</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>44886</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>46309</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45804</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45815</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>46267</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45815</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46254</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45818</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45937</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45926</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>46175</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>46261</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45831</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>45414</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45414</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>45414</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45414</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45860</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45860</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45860</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45860</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45875</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44607</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>44943</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>45957</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45958</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44621</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45107</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45667</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>45667</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46185</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45609</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45979</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>46308</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>46205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45630</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>44841</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45678</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45685</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45825</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>45831</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45713</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>44865</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>46091</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44784</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>44841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>45891</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>44648</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45008</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>46290</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>46260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>45922</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45982</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>44546</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>44841</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>45071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45709</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45081</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45849</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44533</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44958</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>45002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45160</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45280</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45107</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45594</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>45247</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>45548</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>45728</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45155</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45589</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>44908</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>44890</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>44532</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>44518</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45589</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44897</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>44841</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45226</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>45280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44907</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>45103</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44734</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44989</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>45702</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>44978</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45400</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45029</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45602</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44978</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45545</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45027</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44505</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>45069</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44606</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>45001</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45681</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45700</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45697</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45110</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45890</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45086</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44882</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44879</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45899</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45901</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45758</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45491</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>45758</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>44914</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>45104</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45916</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45635</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>46146</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45090</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45922</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44845</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45926</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>46151</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>44855</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45259</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>44879</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45639</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45959</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45959</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45961</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45966</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45966</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45625</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45979</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45979</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45980</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45980</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45980</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45980</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>46164</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45982</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44657</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44657</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45982</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45982</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45982</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45982</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45981</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45986</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45986</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44657</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45545</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>46164</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45054</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44546</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45414</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>46148</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45678</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44852</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>46003</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45056</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>46002</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45156</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46007</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44978</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45548</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45159</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45154</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45371</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45376</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45371</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45817</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45371</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45371</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>46175</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>44546</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>46034</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>46034</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46035</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45709</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>46034</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45611</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45999</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45722</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>46178</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>46178</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46043</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>46043</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>46042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44797</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>46185</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>46185</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>46185</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46185</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>46185</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>46185</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>46078</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>46185</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>46185</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>45219</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44869</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46083</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44841</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>46083</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>46085</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45034</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44999</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44917</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>46099</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>46099</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>46098</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45491</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45155</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44916</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>44994</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>44538</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>44978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46128</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>46129</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>46129</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>46128</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45177</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>46185</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>46205</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44719</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>44918</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45548</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>45420</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44866</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44834</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45609</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>46209</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>46209</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>46211</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>45002</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45520</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>46223</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>46225</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>46225</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44719</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45602</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45029</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>45589</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44719</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45520</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45400</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45559</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45602</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45518</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45568</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>45198</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>45681</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44974</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46280</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>46238</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46238</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>46225</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>44890</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45043</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45159</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45635</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45124</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>46239</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>46240</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44925</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45953</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44895</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44992</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44984</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>46211</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45548</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>46245</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>46216</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46248</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46248</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>46248</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46248</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45804</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>46239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45715</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45715</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45063</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45804</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>46248</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44893</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45804</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45804</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>46247</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46290</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>46248</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>46248</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>46248</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46248</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45306</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>45520</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>46251</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>46253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44731</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45722</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>46253</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>44531</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>46248</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>46227</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>46253</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>46253</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>46253</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46253</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>46253</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>44935</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45182</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45707</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45697</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>46234</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45634</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>46252</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45364</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45400</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45279</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46307</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44900</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44866</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45794</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45980</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>46302</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45794</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>46307</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>46307</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45804</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>46014</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>46308</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>46309</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>46309</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>46309</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>44886</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>46309</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45804</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>45815</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>46267</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45815</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46254</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45818</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45937</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45926</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>46175</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>46261</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45831</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>45414</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45414</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>45414</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45414</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45860</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45860</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45860</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>45860</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45875</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44607</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>44943</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>45957</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45958</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>46185</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45667</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46308</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45609</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>46205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45630</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45678</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45685</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>45825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45106</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44841</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>46091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44865</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44784</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45891</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>45795</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>44648</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>46290</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45008</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>46260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45982</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45849</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45709</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45081</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44841</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45555</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44533</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45063</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>45890</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45043</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44834</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>45901</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45899</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>45602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44882</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>44978</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>45916</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45548</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>46164</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>46164</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45029</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44890</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45926</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>46175</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44917</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>45979</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45709</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>46175</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45602</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45999</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44935</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45400</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45722</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45400</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>46178</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>46178</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>46178</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>46178</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>46178</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>45420</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45160</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>46185</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>46185</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>46185</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44984</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>46185</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>46185</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>46185</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45639</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>46185</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>46185</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45959</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45959</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45961</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45966</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>45966</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>44657</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44657</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44841</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45635</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44999</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44978</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45589</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45980</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45980</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45980</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45979</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45979</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45980</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45982</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45982</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45982</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45982</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>45982</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>46185</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45981</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>46205</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45155</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45110</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45986</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44895</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45090</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45986</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45986</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>46209</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>46209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45155</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>46211</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44978</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45678</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45728</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45548</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45520</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>46002</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>46223</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45697</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>46225</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>46003</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46225</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>46007</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46225</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>46280</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45371</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45371</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>46238</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45371</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45371</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>46239</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45634</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45376</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45817</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44992</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45279</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45364</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46238</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45400</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46034</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>46034</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>44900</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>46240</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44866</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>46035</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45794</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45611</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45794</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>46043</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>46042</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>46043</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>46211</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>46045</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46245</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45953</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45804</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45804</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45804</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>46216</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>46247</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45804</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44886</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>46248</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46248</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>46248</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>46062</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>46248</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>46248</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>46248</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45815</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45815</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>46248</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45818</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>46248</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>46248</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>46253</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>46253</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>46251</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>46253</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>46253</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>46253</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>46253</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>46253</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>46078</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46083</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>46083</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>46085</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45722</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45831</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45034</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45414</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45414</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45414</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45414</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>46248</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>46227</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45491</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>46099</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>46099</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>46252</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>46098</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45860</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45860</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45860</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45860</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45280</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45635</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46129</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45875</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>46128</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>46128</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46307</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>46307</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46129</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>46128</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>46307</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>44916</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45980</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>46308</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>46302</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45804</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>46309</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>46014</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45804</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>44908</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45697</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45198</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>46261</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>46309</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45700</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46309</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>46309</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>46267</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45926</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>46254</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>46175</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45758</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44907</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45758</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>46239</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44866</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45707</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>46316</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45247</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45715</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45715</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>46234</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>46316</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45825</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45589</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46316</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46146</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45054</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>46151</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45259</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44505</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>44890</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44797</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44978</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45609</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45594</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45414</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45002</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>44518</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45027</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>45156</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44719</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>44719</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45625</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>44989</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>45086</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45545</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45191</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44879</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>45681</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45001</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45491</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45306</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44532</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45226</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>44879</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45182</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45280</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>44855</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45219</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44538</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45103</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45559</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45104</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>44531</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45069</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44852</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45548</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44918</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44914</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45124</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44546</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45589</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45029</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44546</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45056</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45518</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45159</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45177</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45198</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45545</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44546</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45159</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45154</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45681</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45702</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>44719</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45107</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>44731</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44657</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>44841</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44893</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>44869</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44974</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45520</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45520</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>45602</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45548</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>44845</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>44925</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>45002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>44606</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45568</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>44607</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44943</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45958</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>45957</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>

--- a/Översikt SORSELE.xlsx
+++ b/Översikt SORSELE.xlsx
@@ -601,7 +601,7 @@
         <v>44693</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45707</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45085</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>44621</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>46205</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45602</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>45414</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45630</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>45635</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>46185</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>45667</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45667</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>46308</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45609</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>46205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45630</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45678</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45685</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45831</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>45825</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45106</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44841</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45635</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45635</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>46091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>45713</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44865</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44784</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45891</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>45795</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>44841</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44518</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>44648</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>46185</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>46290</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45008</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>46260</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>45922</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45982</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45849</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45709</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45081</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45071</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44841</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45555</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44533</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>44550</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44501</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45063</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>45890</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45043</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44834</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45107</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>45901</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45899</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>45602</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44882</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>44978</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>45916</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45548</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>46164</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>46164</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45922</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45029</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>46148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>44890</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45926</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>46175</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>44917</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>45979</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45709</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>46175</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45602</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45999</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44935</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>45400</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45722</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45400</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>46178</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>44897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>46178</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>46178</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>46178</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>46178</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>45420</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45160</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>46185</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>46185</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>46185</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44984</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>46185</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>46185</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>46185</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45639</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>46185</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>46185</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45959</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45959</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45961</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45966</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>45966</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>44657</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44657</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44841</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45635</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44999</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44978</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45589</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45980</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>45980</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45980</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45979</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45979</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45980</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45982</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45982</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45982</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45982</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>45982</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>46185</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45981</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>46205</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45155</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45110</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45986</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44895</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45090</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45986</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45986</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>46209</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>46209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45155</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>46211</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44978</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>45678</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45728</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>45548</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45520</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>46002</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>46223</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45697</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>46225</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>46003</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46225</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>46007</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46225</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>46280</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45371</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45371</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>46238</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45371</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45371</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>46239</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45634</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45376</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45817</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>44992</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>45279</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45364</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46238</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45400</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46034</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46034</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>46034</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>44900</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>46240</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44866</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>46035</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45794</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45611</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45794</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>46043</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>46042</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>46043</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>46211</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>46045</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46245</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45953</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45804</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45804</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45804</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>46216</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>46247</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45804</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44886</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>46248</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46248</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>46248</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>46062</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>46248</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>46248</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>46248</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45815</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45815</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>46248</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45818</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>46248</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>46248</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>46253</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>46253</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>46251</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>46253</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>46253</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>46253</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>46253</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>46253</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>46078</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46083</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>46083</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>46085</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45722</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45831</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45034</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45414</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45414</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45414</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45414</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>46248</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>46227</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45491</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>46099</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>46099</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>46252</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>46098</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45860</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45860</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45860</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45860</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45280</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45635</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46129</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45875</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>46128</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>46128</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46307</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>46307</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>46129</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>46128</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>46307</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>44916</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45980</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>46308</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>46302</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45804</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>46309</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>46014</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45804</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>44908</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45697</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45198</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>46261</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>46309</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45700</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46309</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>46309</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>46267</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>45926</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>46254</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>46175</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45758</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44907</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45758</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>46239</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>44866</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45707</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>46316</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45247</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45715</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45715</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>46234</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>46316</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45825</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45589</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46316</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46146</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45054</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>46151</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45259</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44505</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>44890</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44797</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44978</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45609</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45594</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45414</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>45002</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>44518</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45027</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>45156</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>44734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44719</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>44719</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45625</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>44989</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>45086</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45545</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45191</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>44879</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>45681</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45001</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45491</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45306</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44532</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45226</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>44879</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45182</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45280</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>44855</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45219</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44538</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27803,7 +27803,7 @@
         <v>45103</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45559</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45104</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>44531</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45069</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28183,7 +28183,7 @@
         <v>44852</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45548</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44918</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44914</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45124</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>44546</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45589</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45029</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44546</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28850,7 +28850,7 @@
         <v>45056</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45518</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45159</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45177</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45198</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45545</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44546</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45159</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45154</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45681</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45702</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>44719</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45107</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>44731</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44657</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>44841</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44893</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>44869</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>44974</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45520</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45520</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>45602</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45548</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>44845</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>44925</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>45002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>44606</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45568</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>44607</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44943</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>45958</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>45957</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
